--- a/Models/Молоко/results/Молоко - Результаты прогнозов ХВ средние.xlsx
+++ b/Models/Молоко/results/Молоко - Результаты прогнозов ХВ средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1743.41</v>
+        <v>1926.95</v>
       </c>
       <c r="C2" t="n">
-        <v>1586.41</v>
+        <v>1744.53</v>
       </c>
       <c r="D2" t="n">
-        <v>8.119999999999999</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1823.12</v>
+        <v>1429.97</v>
       </c>
       <c r="C3" t="n">
-        <v>1653.5</v>
+        <v>1284.4</v>
       </c>
       <c r="D3" t="n">
-        <v>10.9</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3617.99</v>
+        <v>2670.18</v>
       </c>
       <c r="C4" t="n">
-        <v>3393.85</v>
+        <v>2350.59</v>
       </c>
       <c r="D4" t="n">
-        <v>13.73</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>331.57</v>
+        <v>228.41</v>
       </c>
       <c r="C5" t="n">
-        <v>289.15</v>
+        <v>192.97</v>
       </c>
       <c r="D5" t="n">
-        <v>10.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2881.2</v>
+        <v>3728.95</v>
       </c>
       <c r="C6" t="n">
-        <v>2521.94</v>
+        <v>3197.45</v>
       </c>
       <c r="D6" t="n">
-        <v>12.9</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.2</v>
+        <v>20.96</v>
       </c>
       <c r="C7" t="n">
-        <v>20.12</v>
+        <v>17.59</v>
       </c>
       <c r="D7" t="n">
-        <v>68.94</v>
+        <v>63.09</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.68</v>
+        <v>3.32</v>
       </c>
       <c r="C8" t="n">
-        <v>2.33</v>
+        <v>2.98</v>
       </c>
       <c r="D8" t="n">
-        <v>14.25</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>656.96</v>
+        <v>655.34</v>
       </c>
       <c r="C9" t="n">
-        <v>606.91</v>
+        <v>611.91</v>
       </c>
       <c r="D9" t="n">
-        <v>9.83</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>747.1799999999999</v>
+        <v>620.64</v>
       </c>
       <c r="C10" t="n">
-        <v>673.1900000000001</v>
+        <v>562.66</v>
       </c>
       <c r="D10" t="n">
-        <v>3.73</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1414.09</v>
+        <v>1384.59</v>
       </c>
       <c r="C11" t="n">
-        <v>1300.5</v>
+        <v>1246.99</v>
       </c>
       <c r="D11" t="n">
-        <v>7.89</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1323.79</v>
+        <v>1055.71</v>
       </c>
       <c r="C12" t="n">
-        <v>1030.95</v>
+        <v>826.9299999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>4.94</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2145.16</v>
+        <v>2039.76</v>
       </c>
       <c r="C13" t="n">
-        <v>1902.5</v>
+        <v>1882.96</v>
       </c>
       <c r="D13" t="n">
-        <v>10.07</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1133.2</v>
+        <v>589.84</v>
       </c>
       <c r="C14" t="n">
-        <v>1070.39</v>
+        <v>483.86</v>
       </c>
       <c r="D14" t="n">
-        <v>31.77</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="15">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="C15" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1747.81</v>
+        <v>1572.07</v>
       </c>
       <c r="C16" t="n">
-        <v>1641.66</v>
+        <v>1453.77</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="17">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>794.77</v>
+        <v>929.4299999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>725.39</v>
+        <v>822.33</v>
       </c>
       <c r="D17" t="n">
-        <v>3.46</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="18">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1077.29</v>
+        <v>656.76</v>
       </c>
       <c r="C18" t="n">
-        <v>917.45</v>
+        <v>558.3200000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>14.54</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="19">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3048.44</v>
+        <v>3707.84</v>
       </c>
       <c r="C19" t="n">
-        <v>2766.88</v>
+        <v>3370.6</v>
       </c>
       <c r="D19" t="n">
-        <v>13.87</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="20">
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5699.74</v>
+        <v>6224.14</v>
       </c>
       <c r="C20" t="n">
-        <v>4997.52</v>
+        <v>5500.6</v>
       </c>
       <c r="D20" t="n">
-        <v>15.95</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="21">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2406.53</v>
+        <v>4236.19</v>
       </c>
       <c r="C21" t="n">
-        <v>2211.13</v>
+        <v>3796.46</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
   </sheetData>
